--- a/结果/问题四_3批次_修复版.xlsx
+++ b/结果/问题四_3批次_修复版.xlsx
@@ -64,7 +64,7 @@
     <t>不均衡度: 87.5%</t>
   </si>
   <si>
-    <t>5架中继无人机</t>
+    <t>6架中继无人机</t>
   </si>
 </sst>
 </file>
@@ -482,16 +482,16 @@
         <v>13</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -505,16 +505,16 @@
         <v>14</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -528,16 +528,16 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -545,7 +545,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
         <v>16</v>

--- a/结果/问题四_3批次_修复版.xlsx
+++ b/结果/问题四_3批次_修复版.xlsx
@@ -1,96 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分组资源" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="官方库存" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源缺口" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>批次</t>
-  </si>
-  <si>
-    <t>服务区数量</t>
-  </si>
-  <si>
-    <t>服务区列表</t>
-  </si>
-  <si>
-    <t>B型电池</t>
-  </si>
-  <si>
-    <t>C型电池</t>
-  </si>
-  <si>
-    <t>B型充电桩</t>
-  </si>
-  <si>
-    <t>C型充电桩</t>
-  </si>
-  <si>
-    <t>批次1</t>
-  </si>
-  <si>
-    <t>批次2</t>
-  </si>
-  <si>
-    <t>批次3</t>
-  </si>
-  <si>
-    <t>总计</t>
-  </si>
-  <si>
-    <t>中继资源</t>
-  </si>
-  <si>
-    <t>S001</t>
-  </si>
-  <si>
-    <t>S002, S005, S006, S009, S011, S014</t>
-  </si>
-  <si>
-    <t>S003, S004, S007, S008, S010, S012, S013, S015</t>
-  </si>
-  <si>
-    <t>不均衡度: 87.5%</t>
-  </si>
-  <si>
-    <t>6架中继无人机</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -105,35 +48,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -421,149 +422,467 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>service_area_ids</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>population</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>mission_count</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>cargo_count</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>completion_min</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>transport_energy_kwh</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>A_uav</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>A_battery</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>A_charger</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>B_uav</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>B_battery</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>B_charger</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>C_uav</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>C_battery</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>C_charger</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>relay_uav</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>relay_ids</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>relay_energy_components</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>S001</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2" t="n">
+        <v>132.0721581834358</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8.375285829114478</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>S002,S005,S006,S009,S011,S014</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>664</v>
+      </c>
+      <c r="D3" t="n">
+        <v>21</v>
+      </c>
+      <c r="E3" t="n">
+        <v>29</v>
+      </c>
+      <c r="F3" t="n">
+        <v>205.6147938843214</v>
+      </c>
+      <c r="G3" t="n">
+        <v>39.88795792388997</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>S003,S004,S007,S008,S010,S012,S013,S015</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>658</v>
+      </c>
+      <c r="D4" t="n">
+        <v>24</v>
+      </c>
+      <c r="E4" t="n">
+        <v>36</v>
+      </c>
+      <c r="F4" t="n">
+        <v>202.9072690360213</v>
+      </c>
+      <c r="G4" t="n">
+        <v>58.01941950379308</v>
+      </c>
+      <c r="H4" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I4" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5">
+      <c r="J4" t="n">
         <v>3</v>
       </c>
-      <c r="E5">
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="n">
         <v>3</v>
       </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>A_uav</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>B_uav</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>C_uav</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>A_battery</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>B_battery</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>C_battery</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>relay_uav</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>relay_energy_components</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>A_uav</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>B_uav</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>C_uav</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>A_battery</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>B_battery</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>C_battery</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>relay_uav</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>relay_energy_components</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/结果/问题四_3批次_修复版.xlsx
+++ b/结果/问题四_3批次_修复版.xlsx
@@ -581,15 +581,11 @@
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -600,29 +596,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S002,S005,S006,S009,S011,S014</t>
+          <t>S002,S003,S004,S005,S007,S008,S009,S010,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>664</v>
+        <v>1171</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="F3" t="n">
         <v>205.6147938843214</v>
       </c>
       <c r="G3" t="n">
-        <v>39.88795792388997</v>
+        <v>91.2075882433958</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
         <v>4</v>
@@ -631,30 +627,30 @@
         <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R01,R02</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -665,50 +661,50 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S003,S004,S007,S008,S010,S012,S013,S015</t>
+          <t>S006,S011</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>658</v>
+        <v>151</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>202.9072690360213</v>
+        <v>175.5971140574344</v>
       </c>
       <c r="G4" t="n">
-        <v>58.01941950379308</v>
+        <v>6.699789184287249</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -858,22 +854,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
         <v>3</v>
       </c>
-      <c r="B2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4</v>
-      </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>

--- a/结果/问题四_3批次_修复版.xlsx
+++ b/结果/问题四_3批次_修复版.xlsx
@@ -542,37 +542,37 @@
         <v>2100</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>132.0721581834358</v>
+        <v>107.6769417160876</v>
       </c>
       <c r="G2" t="n">
-        <v>8.375285829114478</v>
+        <v>7.562048201282888</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
         <v>2</v>
@@ -603,16 +603,16 @@
         <v>1171</v>
       </c>
       <c r="D3" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E3" t="n">
         <v>56</v>
       </c>
       <c r="F3" t="n">
-        <v>205.6147938843214</v>
+        <v>173.6387822549022</v>
       </c>
       <c r="G3" t="n">
-        <v>91.2075882433958</v>
+        <v>82.0186247398732</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -630,13 +630,13 @@
         <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -668,34 +668,34 @@
         <v>151</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>175.5971140574344</v>
+        <v>171.884453886225</v>
       </c>
       <c r="G4" t="n">
-        <v>6.699789184287249</v>
+        <v>8.071934690107373</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
@@ -854,22 +854,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
         <v>3</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>

--- a/结果/问题四_3批次_修复版.xlsx
+++ b/结果/问题四_3批次_修复版.xlsx
@@ -548,7 +548,7 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>107.6769417160876</v>
+        <v>124.2604438794202</v>
       </c>
       <c r="G2" t="n">
         <v>7.562048201282888</v>
@@ -609,10 +609,10 @@
         <v>56</v>
       </c>
       <c r="F3" t="n">
-        <v>173.6387822549022</v>
+        <v>169.7573716381891</v>
       </c>
       <c r="G3" t="n">
-        <v>82.0186247398732</v>
+        <v>82.69839106835188</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -630,7 +630,7 @@
         <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
@@ -668,43 +668,43 @@
         <v>151</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>171.884453886225</v>
+        <v>169.6271142584377</v>
       </c>
       <c r="G4" t="n">
-        <v>8.071934690107373</v>
+        <v>6.085591847195786</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
+      <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="n">
+      <c r="P4" t="n">
         <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -854,22 +854,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
         <v>4</v>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5</v>
-      </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
